--- a/Printers.xlsx
+++ b/Printers.xlsx
@@ -619,6 +619,11 @@
           <t>heavy</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bunny</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>iANAN</t>
@@ -634,6 +639,11 @@
           <t>heavy</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bunny</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>iANAN</t>
@@ -674,6 +684,11 @@
           <t>t</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sisko</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -689,6 +704,11 @@
           <t>t</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sisko</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -699,6 +719,11 @@
           <t>Alan</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sisko</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -712,6 +737,11 @@
       <c r="C14" t="inlineStr">
         <is>
           <t>Alan</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sisko</t>
         </is>
       </c>
     </row>
@@ -908,40 +938,80 @@
       <c r="A2" s="1" t="n">
         <v>0.25</v>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>0.2916666666666667</v>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>0.375</v>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>0.4166666666666667</v>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>0.4583333333333333</v>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>0.5</v>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>0.5416666666666666</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
       </c>
     </row>
     <row r="10">

--- a/Printers.xlsx
+++ b/Printers.xlsx
@@ -484,6 +484,11 @@
           <t>Falan</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sinclair</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -509,6 +514,11 @@
           <t>Falan</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sinclair</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -534,6 +544,11 @@
           <t>Falan</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sinclair</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -559,6 +574,11 @@
           <t>Falan</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sinclair</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -629,6 +649,11 @@
           <t>iANAN</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>body of a calculater</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -649,6 +674,11 @@
           <t>iANAN</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>body of a calculater</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -669,6 +699,11 @@
           <t>iANAN</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>body of a calculater</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -689,6 +724,11 @@
           <t>Sisko</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>body of a calculater</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -709,6 +749,11 @@
           <t>Sisko</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>body of a calculater</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -722,6 +767,11 @@
       <c r="D13" t="inlineStr">
         <is>
           <t>Sisko</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>body of a calculater</t>
         </is>
       </c>
     </row>

--- a/Printers.xlsx
+++ b/Printers.xlsx
@@ -9,6 +9,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FDM" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLA" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DMLS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bamboo printer" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2D Laser Jet Printer" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -47,9 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,6 +472,11 @@
           <t>g</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ejlf</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>EALAN</t>
@@ -494,6 +502,11 @@
           <t>g</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ejlf</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>EALAN</t>
@@ -519,6 +532,11 @@
           <t>g</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ejlf</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>EALAN</t>
@@ -584,6 +602,11 @@
           <t>Falan</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -609,6 +632,11 @@
           <t>Falan</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -634,6 +662,11 @@
           <t>body of a calculater</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -659,6 +692,11 @@
           <t>body of a calculater</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -684,6 +722,11 @@
           <t>body of a calculater</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -709,6 +752,11 @@
           <t>body of a calculater</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -734,6 +782,11 @@
           <t>body of a calculater</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -752,6 +805,11 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>body of a calculater</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alfred</t>
         </is>
       </c>
     </row>
@@ -978,6 +1036,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Bardock</t>
@@ -993,6 +1056,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Bardock</t>
@@ -1008,6 +1076,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Bardock</t>
@@ -1023,6 +1096,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Bardock</t>
@@ -1038,6 +1116,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Bardock</t>
@@ -1053,6 +1136,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Bardock</t>
@@ -1098,6 +1186,11 @@
           <t>t</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cassian</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Bardock</t>
@@ -1113,6 +1206,11 @@
           <t>t</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cassian</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Bardock</t>
@@ -1128,11 +1226,21 @@
           <t>t</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Cassian</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
         <v>0.7083333333333334</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Cassian</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>spid</t>
@@ -1143,6 +1251,11 @@
       <c r="A14" s="1" t="n">
         <v>0.75</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Cassian</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>spid</t>
@@ -1153,6 +1266,11 @@
       <c r="A15" s="1" t="n">
         <v>0.7916666666666666</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Cassian</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>spid</t>
@@ -1163,6 +1281,11 @@
       <c r="A16" s="1" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Cassian</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>spid</t>
@@ -1172,6 +1295,11 @@
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>0.875</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cassian</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1559,4 +1687,286 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>